--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_70_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_70_IN_Piura.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="30">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>57.47</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>37.67</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>4.87</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>22.3879</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1937,11 +1937,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>21.2981</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>95.13</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>1.0898</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>4.87</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2122,11 +2122,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>22.3905</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2245,6 +2245,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2329,6 +2330,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2373,6 +2375,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="144" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2897,11 +2900,11 @@
       </c>
       <c r="B21" s="32">
         <f>SUM(B10:B20)</f>
-        <v/>
+        <v>481.17</v>
       </c>
       <c r="C21" s="23">
         <f>SUM(C10:C20)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
@@ -2911,19 +2914,19 @@
       <c r="E21" s="17" t="inlineStr"/>
       <c r="F21" s="17">
         <f>ROUND(AVERAGE(F10:F20),2)</f>
-        <v/>
+        <v>29.39</v>
       </c>
       <c r="G21" s="22">
         <f>ROUND(AVERAGE(G10:G20),4)</f>
-        <v/>
+        <v>0.5435</v>
       </c>
       <c r="H21" s="23">
         <f>ROUND(AVERAGE(H10:H20),2)</f>
-        <v/>
+        <v>73.58</v>
       </c>
       <c r="I21" s="23">
         <f>ROUND(AVERAGE(I10:I20),2)</f>
-        <v/>
+        <v>32.8</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
